--- a/Sprint-3/Ticket_41794528_My_Account_Holds/My_Holds_Test_Cases.xlsx
+++ b/Sprint-3/Ticket_41794528_My_Account_Holds/My_Holds_Test_Cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Holds Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,441 +397,1608 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>tc_id</v>
+        <v>Test Case ID</v>
       </c>
       <c r="B1" t="str">
-        <v>module</v>
+        <v>Module</v>
       </c>
       <c r="C1" t="str">
-        <v>test_title</v>
+        <v>Auth Matrix</v>
       </c>
       <c r="D1" t="str">
-        <v>preconditions</v>
+        <v>Test Scenario / Title</v>
       </c>
       <c r="E1" t="str">
-        <v>test_steps</v>
+        <v>Preconditions</v>
       </c>
       <c r="F1" t="str">
-        <v>expected_result</v>
+        <v>Test Steps</v>
       </c>
       <c r="G1" t="str">
-        <v>actual_result</v>
+        <v>Expected Result (Figma Spec / Frame 621)</v>
       </c>
       <c r="H1" t="str">
-        <v>status</v>
+        <v>Actual Result (mcstaging2 Live)</v>
       </c>
       <c r="I1" t="str">
-        <v>severity</v>
+        <v>Status</v>
       </c>
       <c r="J1" t="str">
-        <v>compliance</v>
+        <v>Severity</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Compliance</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>TC-HOLDS-01</v>
+        <v>TC-GW-HOLDS-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Authentication &amp; Access</v>
+        <v>Authentication &amp; Route Access</v>
       </c>
       <c r="C2" t="str">
-        <v>Direct URL Access as Logged-Out Guest</v>
+        <v>Guest (Logged Out)</v>
       </c>
       <c r="D2" t="str">
-        <v>User is not logged in</v>
-      </c>
-      <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate directly to /gw_orders/hold/index/
-2. Observe redirection and page behavior</v>
-      </c>
-      <c r="F2" t="str">
-        <v>User is redirected to Customer Login page (/customer/account/login/) with session notice</v>
+        <v>Verify Direct URL Access Redirection to Customer Login</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Public unauthenticated guest session on US Staging (mcstaging2.globewest.com)</v>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open browser in incognito / logged-out state
+2. Navigate directly to https://mcstaging2.globewest.com/gw_orders/hold/index/
+3. Observe HTTP status code and redirect target</v>
       </c>
       <c r="G2" t="str">
-        <v>Redirects to customer login page with notice</v>
+        <v>System must strictly prohibit unauthorized access to trade account portals and redirect the guest to /customer/account/login/ with an informational message.</v>
       </c>
       <c r="H2" t="str">
-        <v>PASS</v>
+        <v>Page redirects immediately to /customer/account/login/ with standard session prompt.</v>
       </c>
       <c r="I2" t="str">
-        <v>High</v>
+        <v>PASS</v>
       </c>
       <c r="J2" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K2" t="str">
         <v>AGENTS.md Rule 3 Dual-Auth</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>TC-HOLDS-02</v>
+        <v>TC-GW-HOLDS-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Authentication &amp; Access</v>
+        <v>Authentication &amp; Route Access</v>
       </c>
       <c r="C3" t="str">
-        <v>Authenticated Trade Customer Access</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D3" t="str">
-        <v>User logged in with Trade Customer credentials</v>
-      </c>
-      <c r="E3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Login with trade account
-2. Navigate to /gw_orders/hold/index/</v>
-      </c>
-      <c r="F3" t="str">
-        <v>My Holds dashboard loads with breadcrumbs, left account navigation, and table container</v>
+        <v>Verify Authenticated Trade Customer Access to My Holds Portal</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Active session with US Trade account credentials (deepali.londhe@overdose.digital)</v>
+      </c>
+      <c r="F3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Log in with US Trade account
+2. Navigate to /gw_orders/hold/index/
+3. Verify HTTP 200 response and visual elements</v>
       </c>
       <c r="G3" t="str">
-        <v>My Holds dashboard loads successfully for Trade account</v>
+        <v>My Holds portal loads cleanly with HTTP 200. Displays page title 'My Holds', subtitle, status filter tabs, search bar, holds table, and FAQ module.</v>
       </c>
       <c r="H3" t="str">
-        <v>PASS</v>
+        <v>Dashboard loads successfully with HTTP 200 and all core dashboard containers.</v>
       </c>
       <c r="I3" t="str">
-        <v>High</v>
+        <v>PASS</v>
       </c>
       <c r="J3" t="str">
-        <v>Frame 621</v>
+        <v>P1 - High</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Frame 621 Specification</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>TC-HOLDS-03</v>
+        <v>TC-GW-HOLDS-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Status Filter Tabs</v>
+        <v>Account Sidebar Navigation</v>
       </c>
       <c r="C4" t="str">
-        <v>Default Active Filter Tab (ACTIVE)</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D4" t="str">
-        <v>User on My Holds page</v>
-      </c>
-      <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect default filter tabs on initial load
-2. Check active class and computed styles</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Filter tabs display 'ACTIVE' and 'INACTIVE'. 'ACTIVE' tab is selected by default with dark brown solid pill styling (#2B1D16 / rgb(56, 28, 18)) and white text</v>
+        <v>Verify Active Menu Item Highlighting on 'Holds' Link</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Trade Customer on /gw_orders/hold/index/ desktop viewport</v>
+      </c>
+      <c r="F4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate left sidebar menu under 'MY ACCOUNT'
+2. Inspect CSS classes and computed styles of the 'Holds' link
+3. Compare against adjacent links (Quotes, Orders)</v>
       </c>
       <c r="G4" t="str">
-        <v>Renders 'ACTIVE' (is-active, dark background, white text) and 'INACTIVE'</v>
+        <v>'Holds' link receives active styling (class 'current' / dark brown color rgb(56, 28, 18) and bold weight), clearly identifying current section.</v>
       </c>
       <c r="H4" t="str">
-        <v>PASS</v>
+        <v>'Holds' element has 'nav item current item--counter item--holds' with active visual indicator.</v>
       </c>
       <c r="I4" t="str">
-        <v>High</v>
+        <v>PASS</v>
       </c>
       <c r="J4" t="str">
-        <v>Frame 621 Rule 1</v>
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K4" t="str">
+        <v>UI Navigation Hierarchy</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>TC-HOLDS-04</v>
+        <v>TC-GW-HOLDS-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Status Filter Tabs</v>
+        <v>Account Sidebar Navigation</v>
       </c>
       <c r="C5" t="str">
-        <v>Tab Switching State Transition</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D5" t="str">
-        <v>User on My Holds page</v>
-      </c>
-      <c r="E5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click 'INACTIVE' tab
-2. Verify table updates and active tab changes to 'INACTIVE'
-3. Click back to 'ACTIVE'</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Active styling switches cleanly between ACTIVE and INACTIVE tabs; table records filter accordingly</v>
+        <v>Verify Hold Count Badge Math and Pill Display (Developer Update)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Trade Customer with 3 Active Holds and 2 Inactive Holds on record</v>
+      </c>
+      <c r="F5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect the blue count badge (.item__counter) rendered adjacent to 'Holds' in left navigation
+2. Verify displayed numeric value
+3. Check border-radius pill styling</v>
       </c>
       <c r="G5" t="str">
-        <v>Tab toggles cleanly between ACTIVE and INACTIVE</v>
+        <v>Badge renders total count '5' (sum of 3 Active + 2 Inactive holds) in a pill-shaped container, verifying developer Vinod's badge update.</v>
       </c>
       <c r="H5" t="str">
-        <v>PASS</v>
+        <v>Badge renders '5' inside .item__counter matching total holds count. Verified fixed.</v>
       </c>
       <c r="I5" t="str">
-        <v>Medium</v>
+        <v>PASS</v>
       </c>
       <c r="J5" t="str">
-        <v>Frame 621</v>
+        <v>P1 - High</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Frame 621 Counter Badge Spec</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>TC-HOLDS-05</v>
+        <v>TC-GW-HOLDS-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Search Component</v>
+        <v>Status Filter Tabs</v>
       </c>
       <c r="C6" t="str">
-        <v>Horizontal Inline Search Alignment</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D6" t="str">
-        <v>User on My Holds page</v>
-      </c>
-      <c r="E6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect positioning of search input relative to filter tabs
-2. Check placeholder and search icon</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Search input sits horizontally on the same row adjacent to filter tabs with magnifying glass icon</v>
+        <v>Verify Default 'ACTIVE' Filter Tab Selection &amp; Pill Styling</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Trade Customer on My Holds initial dashboard load</v>
+      </c>
+      <c r="F6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect filter buttons above table
+2. Check active class on 'ACTIVE' button
+3. Inspect computed background-color and text color</v>
       </c>
       <c r="G6" t="str">
-        <v>Search input is aligned inline on the same horizontal row beside filter tabs</v>
+        <v>'ACTIVE' tab selected by default with solid dark brown background (#2B1D16 / rgb(56, 28, 18)) and white text (#FFFFFF). 'INACTIVE' is unselected with neutral outline.</v>
       </c>
       <c r="H6" t="str">
-        <v>PASS</v>
+        <v>'ACTIVE' has class 'account-listing-ui__filters__filter is-active' with background rgb(56, 28, 18) and white text.</v>
       </c>
       <c r="I6" t="str">
-        <v>Medium</v>
+        <v>PASS</v>
       </c>
       <c r="J6" t="str">
-        <v>Figma Artboard</v>
+        <v>P1 - High</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Frame 621 Rule 1</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>TC-HOLDS-06</v>
+        <v>TC-GW-HOLDS-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Table Architecture</v>
+        <v>Status Filter Tabs</v>
       </c>
       <c r="C7" t="str">
-        <v>Column Reduction &amp; Redundant Actions Column</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D7" t="str">
-        <v>User on My Holds page desktop view</v>
-      </c>
-      <c r="E7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect table headers on desktop view
-2. Count columns and check for standalone Actions column</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Table displays 7 columns (HOLD, EXP. DATE, CUST PO#, ORDER NAME, CLIENT NAME, STATUS, TOTAL). Per Frame 621, if only view action exists, hide separate Actions column and make Hold # clickable</v>
+        <v>Verify Tab Switching State Transition to 'INACTIVE'</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Trade Customer on My Holds page with active tab selected</v>
+      </c>
+      <c r="F7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click 'INACTIVE' filter tab
+2. Observe active styling switch
+3. Verify table content updates dynamically to display inactive holds</v>
       </c>
       <c r="G7" t="str">
-        <v>Table displays 8 columns including a redundant 'ACTIONS' column</v>
+        <v>Active styling switches cleanly to 'INACTIVE' tab. Table updates to display inactive/expired holds (2 records) without page reloading or UI breakage.</v>
       </c>
       <c r="H7" t="str">
-        <v>FAIL</v>
+        <v>'INACTIVE' tab activates; table filters cleanly to display 2 inactive records.</v>
       </c>
       <c r="I7" t="str">
-        <v>High</v>
+        <v>PASS</v>
       </c>
       <c r="J7" t="str">
-        <v>Frame 621 Rule 2 &amp; 4</v>
+        <v>P1 - High</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Frame 621 Functional Spec</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>TC-HOLDS-07</v>
+        <v>TC-GW-HOLDS-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Table Architecture</v>
+        <v>Status Filter Tabs</v>
       </c>
       <c r="C8" t="str">
-        <v>Header Label Typo ('CUST P0#' zero vs letter O)</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D8" t="str">
-        <v>User on My Holds page desktop view</v>
-      </c>
-      <c r="E8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect column 3 header text in DOM
-2. Check character representation</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Header label displays 'CUST PO#' with capital letter 'O'</v>
+        <v>Verify Switching Back from 'INACTIVE' to 'ACTIVE' Tab</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Trade Customer on 'INACTIVE' tab view</v>
+      </c>
+      <c r="F8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click 'ACTIVE' filter tab
+2. Verify tab styling returns to 'ACTIVE'
+3. Verify table displays the 3 active hold records</v>
       </c>
       <c r="G8" t="str">
-        <v>Header label displays 'CUST P0#' with number zero '0' instead of capital letter 'O'</v>
+        <v>'ACTIVE' tab regains dark brown active styling. Table re-filters to display active holds.</v>
       </c>
       <c r="H8" t="str">
-        <v>FAIL</v>
+        <v>Tab transitions smoothly back to ACTIVE state with 3 active records.</v>
       </c>
       <c r="I8" t="str">
-        <v>Medium</v>
+        <v>PASS</v>
       </c>
       <c r="J8" t="str">
-        <v>Figma Spec</v>
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Frame 621 State Management</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>TC-HOLDS-08</v>
+        <v>TC-GW-HOLDS-008</v>
       </c>
       <c r="B9" t="str">
-        <v>Editorial &amp; Content</v>
+        <v>Status Filter Tabs</v>
       </c>
       <c r="C9" t="str">
-        <v>Sub-heading Feature Description Copy</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D9" t="str">
-        <v>User on My Holds page</v>
-      </c>
-      <c r="E9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Read sub-heading description copy below 'My Holds' title
-2. Verify presence and feature introduction</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Displays feature intro copy below title ('A product hold reserves your favourite items for 2 business days.') consistent with Figma layout</v>
+        <v>Verify Inactive Holds Advisory Banner Rendering</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Trade Customer switched to 'INACTIVE' tab</v>
+      </c>
+      <c r="F9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. View top of inactive holds table
+2. Inspect advisory notice text for expired/inactive items</v>
       </c>
       <c r="G9" t="str">
-        <v>Introductory copy is present and accurately describes product hold behavior</v>
+        <v>Advisory text displays informing the user that holds expire after 2 business days and how to request re-activation.</v>
       </c>
       <c r="H9" t="str">
-        <v>PASS</v>
+        <v>Informational banner renders cleanly on inactive view.</v>
       </c>
       <c r="I9" t="str">
-        <v>Low</v>
+        <v>PASS</v>
       </c>
       <c r="J9" t="str">
-        <v>Frame 621 / Layout Spec</v>
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Frame 621 UX Notification Spec</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>TC-HOLDS-09</v>
+        <v>TC-GW-HOLDS-009</v>
       </c>
       <c r="B10" t="str">
-        <v>FAQ Module</v>
+        <v>Search Component</v>
       </c>
       <c r="C10" t="str">
-        <v>FAQ Accordion Presence &amp; Default Closed State</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D10" t="str">
-        <v>User on My Holds page</v>
-      </c>
-      <c r="E10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll down to Frequently Asked Questions section
-2. Inspect initial visibility of answers</v>
-      </c>
-      <c r="F10" t="str">
-        <v>FAQ section is present below table; all accordion items are closed by default</v>
+        <v>Verify Horizontal Inline Search Input Alignment with Filter Tabs</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Trade Customer on desktop viewport (1440px)</v>
+      </c>
+      <c r="F10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect positioning of search input box relative to filter tabs
+2. Check placeholder and magnifying glass icon placement</v>
       </c>
       <c r="G10" t="str">
-        <v>FAQ section is present; all accordions are closed on page load</v>
+        <v>Search input sits horizontally on the same row adjacent to filter tabs with inset magnifying glass search icon per Figma mockup.</v>
       </c>
       <c r="H10" t="str">
-        <v>PASS</v>
+        <v>Search bar is aligned inline horizontally beside tabs with search icon.</v>
       </c>
       <c r="I10" t="str">
-        <v>Medium</v>
+        <v>PASS</v>
       </c>
       <c r="J10" t="str">
-        <v>Frame 621 FAQ Spec</v>
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Figma Artboard Alignment</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
-        <v>TC-HOLDS-10</v>
+        <v>TC-GW-HOLDS-010</v>
       </c>
       <c r="B11" t="str">
-        <v>FAQ Module</v>
+        <v>Search Component</v>
       </c>
       <c r="C11" t="str">
-        <v>FAQ Accordion Single-Open Auto-Collapse Rule</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D11" t="str">
-        <v>User on My Holds page</v>
-      </c>
-      <c r="E11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click FAQ item 1 to expand
-2. Click FAQ item 2
-3. Verify whether FAQ item 1 collapses automatically</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Only one accordion remains open at a time; expanding item 2 automatically collapses item 1</v>
+        <v>Verify Filter Table Records by Specific Hold Number</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Multiple active holds present in table</v>
+      </c>
+      <c r="F11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Type Hold # '175' into search input
+2. Press Enter or click search button
+3. Observe table rows</v>
       </c>
       <c r="G11" t="str">
-        <v>Expanding item 2 automatically collapsed item 1 (single-open rule strictly enforced)</v>
+        <v>Table updates to show only the matching Hold # 175 row. Non-matching records are excluded from view.</v>
       </c>
       <c r="H11" t="str">
-        <v>PASS</v>
+        <v>Table filters dynamically to show Hold # 175.</v>
       </c>
       <c r="I11" t="str">
-        <v>High</v>
+        <v>PASS</v>
       </c>
       <c r="J11" t="str">
-        <v>Frame 621 FAQ Spec</v>
+        <v>P1 - High</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Search Functionality</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>TC-HOLDS-11</v>
+        <v>TC-GW-HOLDS-011</v>
       </c>
       <c r="B12" t="str">
-        <v>Customer Support Block</v>
+        <v>Search Component</v>
       </c>
       <c r="C12" t="str">
-        <v>Support Block Layout &amp; Design Matching</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D12" t="str">
-        <v>User on My Holds page</v>
-      </c>
-      <c r="E12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect 'Need help? Contact our sales team' block below FAQs
-2. Verify contact phone, email, and layout against Figma Frame 621</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Support block displays 'Need help? Contact our sales team', phone 'P: +613 9518 1600', and email 'E: salessupport@globewest.com.au' matching Figma Frame 621 mockup text</v>
+        <v>Verify Search Execution by Customer PO# &amp; Order Name</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Trade Customer on My Holds dashboard</v>
+      </c>
+      <c r="F12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Enter PO identifier 'PO-4518' or Order Name 'Coastal Cafe Refresh' into search
+2. Submit search query</v>
       </c>
       <c r="G12" t="str">
-        <v>Matches Figma Frame 621 design mockup identically; configurable via Magento CMS static block for future US contact updates</v>
+        <v>Search matches PO# and Order Name fields and returns the corresponding record.</v>
       </c>
       <c r="H12" t="str">
-        <v>PASS</v>
+        <v>Matching record is returned in table.</v>
       </c>
       <c r="I12" t="str">
-        <v>Low</v>
+        <v>PASS</v>
       </c>
       <c r="J12" t="str">
-        <v>Frame 621 Figma Spec</v>
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Search Functionality</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>TC-HOLDS-12</v>
+        <v>TC-GW-HOLDS-012</v>
       </c>
       <c r="B13" t="str">
-        <v>Mobile Responsive View</v>
+        <v>Search Component</v>
       </c>
       <c r="C13" t="str">
-        <v>Mobile Viewport (390x844) Layout &amp; Table Display</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D13" t="str">
-        <v>Mobile viewport 390x844 (iPhone 14/15/16)</v>
-      </c>
-      <c r="E13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load /gw_orders/hold/index/ in mobile viewport
-2. Inspect filter tabs, search bar, table columns, and accordions</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Layout stacks cleanly without horizontal overflow; table shows essential mobile columns (HOLD, DATE, STATUS, TOTAL, ACTIONS)</v>
+        <v>Verify Search Reset &amp; Restoring Full Table View</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Search query currently active and table filtered</v>
+      </c>
+      <c r="F13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Clear all text from search input box
+2. Submit empty query / press Enter
+3. Check table rows</v>
       </c>
       <c r="G13" t="str">
-        <v>Mobile layout stacks cleanly; table displays 5 columns with horizontal scroll and responsive card view</v>
+        <v>Table resets to show all 3 active hold records without requiring full page refresh.</v>
       </c>
       <c r="H13" t="str">
-        <v>PASS</v>
+        <v>Table resets and displays all active records.</v>
       </c>
       <c r="I13" t="str">
-        <v>High</v>
+        <v>PASS</v>
       </c>
       <c r="J13" t="str">
-        <v>Mobile Artboard</v>
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Search Functionality</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>TC-GW-HOLDS-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Search Component</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Verify Empty Search Results State Handling</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Trade Customer on My Holds dashboard</v>
+      </c>
+      <c r="F14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Enter non-existent keyword (e.g. 'XYZ99999NONEXISTENT')
+2. Execute search
+3. Observe table body</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Table body displays clear empty state messaging indicating no matching holds were found.</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Displays empty state notice 'Table is empty!' / 'No records found'.</v>
+      </c>
+      <c r="I14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J14" t="str">
+        <v>P3 - Low</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Empty State Standard</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>TC-GW-HOLDS-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Table Architecture</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Verify Desktop Column Sequence &amp; Headers Count (Frame 621 Rule)</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Trade Customer on desktop viewport</v>
+      </c>
+      <c r="F15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect table thead element
+2. Verify headers: HOLD, EXP. DATE, CUST PO#, ORDER NAME, CLIENT NAME, STATUS, TOTAL, ACTIONS
+3. Cross-reference Frame 621 multi-action rule</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Frame 621 rule: 'if the only action available is view, hide column; otherwise actions housed under dropdown for both mobile + desktop'. If multiple actions exist, 8 columns with Actions column is expected.</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Table renders 8 columns with dedicated 'ACTIONS' column housing multi-action dropdown. Conforms to multi-action rule.</v>
+      </c>
+      <c r="I15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J15" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Frame 621 Rule 2 &amp; 4</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>TC-GW-HOLDS-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Table Architecture</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Verify Customer PO# Column Header Label Typo ('CUST P0#' Zero vs 'CUST PO#')</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Trade Customer on My Holds desktop view</v>
+      </c>
+      <c r="F16" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect 3rd column header text in DOM
+2. Check whether character after 'P' is digit '0' or letter 'O'
+3. Compare against data rows underneath</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Header should read 'CUST PO#' (letter 'O' for Purchase Order). Both Figma mockup and live code contain 'CUST P0#' with numeric zero '0', representing a design spec typo.</v>
+      </c>
+      <c r="H16" t="str">
+        <v>DOM renders 'CUST P0#' with number zero '0'. Matches Figma mockup, but both contain typo.</v>
+      </c>
+      <c r="I16" t="str">
+        <v>FAIL (Design Typo ⚠️)</v>
+      </c>
+      <c r="J16" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Commercial Data Integrity</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>TC-GW-HOLDS-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Table Architecture</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Verify Table Row Actions Dropdown Menu Interaction</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Active hold record row with Actions trigger</v>
+      </c>
+      <c r="F17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click 'Actions ⌵' button in ACTIONS column
+2. Inspect dropdown options (View, Modify / Confirm)
+3. Click outside dropdown to dismiss</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Dropdown opens smoothly displaying contextual actions: 'View Hold', 'Modify / Confirm Hold'. Dismisses cleanly when clicking outside.</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Dropdown expands showing action options; dismisses cleanly on backdrop click.</v>
+      </c>
+      <c r="I17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J17" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Frame 621 Rule 4</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>TC-GW-HOLDS-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Table Architecture</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Verify Clickable Hold # Link Navigation to Hold Detail View</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Trade Customer on My Holds page with active records</v>
+      </c>
+      <c r="F18" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click on Hold # link '175'
+2. Observe URL and destination page</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Directly navigates to the Hold View/Details page (/gw_orders/hold/view/hold_id/175/) displaying hold item breakdown and product lines.</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Direct link navigates to hold detail summary page.</v>
+      </c>
+      <c r="I18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J18" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Frame 621 Navigation Spec</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>TC-GW-HOLDS-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Table Data Integrity</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Verify Hold Status Badge Pill Styling &amp; Color Coding</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Rows with status values ('Active', 'Expired')</v>
+      </c>
+      <c r="F19" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect STATUS column cell in DOM
+2. Verify pill border-radius, background, and font styling</v>
+      </c>
+      <c r="G19" t="str">
+        <v>'Active' status renders in a pill-shaped container with distinct green/neutral accent; 'Expired' renders in subdued styling.</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Status renders with pill borders and clear visual status distinction.</v>
+      </c>
+      <c r="I19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J19" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K19" t="str">
+        <v>AGENTS.md Rule 1 Micro-UI</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC-GW-HOLDS-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Data Localization</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Verify Date Format Localization for US Storefront (US MM/DD/YYYY vs AU DD/MM/YY) [ACTIVE DEFECT]</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Trade Customer on US Staging (/gw_orders/hold/index/)</v>
+      </c>
+      <c r="F20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect EXP. DATE column values in table rows (e.g. 14/10/26)
+2. Cross-reference Frame 621 explicit directive</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Frame 621 explicitly states: 'ensure dates displayed are in USA format' (MM/DD/YYYY or MM/DD/YY, e.g. 10/14/26 for Oct 14).</v>
+      </c>
+      <c r="H20" t="str">
+        <v>FAIL: Live storefront leaks Australian date format DD/MM/YY ('14/10/26', '07/10/26', '02/10/26'). Day 14 cannot represent a month in US standard.</v>
+      </c>
+      <c r="I20" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="J20" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Frame 621 Explicit Directive</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-GW-HOLDS-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Financial &amp; Currency</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Verify Total Column Currency Symbol ($ USD) &amp; 2-Decimal Precision</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Trade Customer on US Staging My Holds page</v>
+      </c>
+      <c r="F21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect TOTAL column values in all rows
+2. Verify currency symbol ($) and thousands comma separator</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Total amounts formatted as USD currency with dollar sign ($), thousands commas, and two decimals (e.g. $2,451.00, $12,920.99, $15,296.00).</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Currency values correctly formatted as $2,451.00, $12,920.99, $15,296.00 with proper symbols.</v>
+      </c>
+      <c r="I21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J21" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K21" t="str">
+        <v>US Storefront Pricing Standard</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-GW-HOLDS-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Editorial &amp; Content</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Verify Urgency Expiration Notification Banner Rendering</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Holds present nearing expiration threshold</v>
+      </c>
+      <c r="F22" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect advisory banner text below table
+2. Verify exact copy phrasing</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Displays banner text: 'Your hold is almost due to expire. Please confirm the order today to prevent your products being released'.</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Urgency banner is rendered with exact expected notification copy.</v>
+      </c>
+      <c r="I22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J22" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Frame 621 Notification Spec</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>TC-GW-HOLDS-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Table Pager &amp; Summary</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Verify Active Holds Item Count Summary Label ('3 Items')</v>
+      </c>
+      <c r="E23" t="str">
+        <v>3 active hold rows rendered in table</v>
+      </c>
+      <c r="F23" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect summary count text below table
+2. Verify number matches displayed rows count</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Displays '3 Items' matching the 3 rendered rows.</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Renders '3 Items' corresponding accurately to row count.</v>
+      </c>
+      <c r="I23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J23" t="str">
+        <v>P3 - Low</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Table Summary Standard</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>TC-GW-HOLDS-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Editorial &amp; Localization</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Verify Sub-heading Copy US English Spelling Compliance ('favorite' vs 'favourite') [ACTIVE DEFECT]</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Trade Customer on US Staging My Holds page</v>
+      </c>
+      <c r="F24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Read subtitle copy below 'My Holds' title
+2. Inspect spelling of word 'favourite'</v>
+      </c>
+      <c r="G24" t="str">
+        <v>US storefront must use US American English spelling: 'A product hold reserves your favorite items for 2 business days.'</v>
+      </c>
+      <c r="H24" t="str">
+        <v>FAIL: Subtitle uses Australian/British spelling 'favourite': 'A product hold reserves your favourite items for 2 business days.'</v>
+      </c>
+      <c r="I24" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="J24" t="str">
+        <v>P3 - Low</v>
+      </c>
+      <c r="K24" t="str">
+        <v>AGENTS.md Rule 4 Editorial Standards</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>TC-GW-HOLDS-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>FAQ Accordion</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Verify FAQ Accordions Default Collapsed / Closed State</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Trade Customer on My Holds page</v>
+      </c>
+      <c r="F25" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Scroll down to 'Frequently Asked Questions' section
+2. Inspect visibility of answer bodies</v>
+      </c>
+      <c r="G25" t="str">
+        <v>All FAQ questions are collapsed by default on page load. Answer content is concealed until user clicks to expand.</v>
+      </c>
+      <c r="H25" t="str">
+        <v>All FAQ items are collapsed by default on initial page render.</v>
+      </c>
+      <c r="I25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J25" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Frame 621 FAQ Spec</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>TC-GW-HOLDS-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>FAQ Accordion</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Verify FAQ Single-Open Auto-Collapse Accordion Logic</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Trade Customer at FAQ section</v>
+      </c>
+      <c r="F26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click FAQ item 1 to expand answer
+2. Click FAQ item 2
+3. Observe whether FAQ item 1 auto-collapses</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Frame 621 single-open rule enforced: Expanding FAQ item 2 automatically collapses FAQ item 1 so only one item remains open.</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Verified in headed Chrome: Expanding item 2 immediately auto-collapses item 1.</v>
+      </c>
+      <c r="I26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J26" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Frame 621 FAQ Logic Spec</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>TC-GW-HOLDS-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Customer Support Block</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Verify Sales Support Contact Phone US Localization (+613 vs US Toll-Free) [ACTIVE DEFECT]</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Trade Customer at bottom support block of My Holds</v>
+      </c>
+      <c r="F27" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect 'Need help? Contact our sales team' section
+2. Check phone number prefix and email address</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Should display US-localized contact details (US phone number / US support email) for US market.</v>
+      </c>
+      <c r="H27" t="str">
+        <v>FAIL: Displays Australian contact details: 'P: +613 9518 1600' and 'sales@globewest.com'.</v>
+      </c>
+      <c r="I27" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="J27" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K27" t="str">
+        <v>US Storefront Localization</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>TC-GW-HOLDS-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Mobile Responsiveness</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Verify Mobile Table Column Sequence at 390px Viewport [ACTIVE DEFECT]</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Browser viewport set to 390x844 (iPhone 14/15/16)</v>
+      </c>
+      <c r="F28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect mobile table column order
+2. Compare against Figma mobile artboard (HOLD | DATE | TOTAL | STATUS | ACTIONS)</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Columns sequenced as: HOLD | DATE | TOTAL | STATUS | ACTIONS.</v>
+      </c>
+      <c r="H28" t="str">
+        <v>FAIL: Sequence is reversed: HOLD | DATE | STATUS | TOTAL | ACTIONS (STATUS placed before TOTAL).</v>
+      </c>
+      <c r="I28" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="J28" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Mobile Artboard Parity</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>TC-GW-HOLDS-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Mobile Responsiveness</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Verify Mobile Actions Dropdown Button Clipping &amp; Overflow [ACTIVE DEFECT]</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Browser viewport width 390px</v>
+      </c>
+      <c r="F29" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect right boundary of mobile table
+2. Verify visibility of column 5 'Actions' button</v>
+      </c>
+      <c r="G29" t="str">
+        <v>All columns and CTA buttons fit comfortably or have smooth horizontal scroll without clipped text.</v>
+      </c>
+      <c r="H29" t="str">
+        <v>FAIL: 'Actions' button overflows right edge and is clipped (only partial text 'Ac' visible).</v>
+      </c>
+      <c r="I29" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="J29" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Mobile UX &amp; Touch Accessibility</v>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>TC-GW-HOLDS-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Mobile Ergonomics</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Verify Mobile Touch Targets for Filter Tabs and FAQ Headers (&gt;= 44px)</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Mobile viewport 390px</v>
+      </c>
+      <c r="F30" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Measure computed height and padding of filter buttons
+2. Measure FAQ header tap targets</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Interactive elements meet minimum touch target recommendations of 44x44px for effortless mobile tapping.</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Filter tabs and FAQ triggers meet minimum touch target standards.</v>
+      </c>
+      <c r="I30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J30" t="str">
+        <v>P3 - Low</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Mobile Ergonomics &amp; WCAG</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>TC-GW-HOLDS-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Breadcrumb Navigation</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Verify Breadcrumb Trail Hierarchy and Link Destinations</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Trade Customer on My Holds page</v>
+      </c>
+      <c r="F31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect breadcrumb trail at top of page
+2. Verify link hierarchy: Home &gt; My Account &gt; My Holds
+3. Click 'My Account'</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Trail displays Home &gt; My Account &gt; My Holds. Clicking 'My Account' navigates to /customer/account/. 'My Holds' is active.</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Breadcrumb trail renders correctly with valid navigational links.</v>
+      </c>
+      <c r="I31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J31" t="str">
+        <v>P3 - Low</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Global Navigation Standard</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>TC-GW-HOLDS-ADMIN-001</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Admin Authentication &amp; Scope</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Verify Magento Admin Login &amp; USA Website Scope Isolation for Holds Management</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Valid Magento Admin credentials (deepali.londhe@overdose.digital / 2Ho770ZEeX7v).</v>
+      </c>
+      <c r="F32" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to https://mcstaging2.globewest.com.au/godmode/admin/
+2. Enter authorized credentials and submit
+3. Verify successful redirect to Admin Dashboard
+4. Click Scope switcher dropdown in header
+5. Select USA Website / USA Store View and confirm active scope header</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Admin authenticates successfully; scope switcher allows switching to USA Website to isolate US market configuration from Australian baseline.</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Admin login verified functional; USA Website scope switcher is active and selectable.</v>
+      </c>
+      <c r="I32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J32" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K32" t="str">
+        <v>AGENTS.md Rule 3 Dual-Store Scope</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>TC-GW-HOLDS-ADMIN-002</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Admin Content Configuration</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Verify Admin Holds Title &amp; Subtitle Copy Configuration and US Spelling Localization [DEFECT]</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Admin logged in under USA Website scope.</v>
+      </c>
+      <c r="F33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Stores &gt; Configuration &gt; OVERDOSE &gt; Customer Account Content Configs
+2. Expand B2b Account Content fieldset
+3. Locate B2b Holds Title and B2b Holds Text fields
+4. Inspect current configured string for B2b Holds Text
+5. Compare with frontend /gw_orders/hold/index/ subtitle copy</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Admin provides dedicated editable fields for Holds title and subtitle; copy for USA scope must use US English spelling (favorite instead of Australian favourite).</v>
+      </c>
+      <c r="H33" t="str">
+        <v>FAIL: Admin configuration currently contains Australian spelling: "A product hold reserves your favourite items for 2 business days...", which leaks directly to US storefront.</v>
+      </c>
+      <c r="I33" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="J33" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K33" t="str">
+        <v>US Storefront Editorial Localization</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>TC-GW-HOLDS-ADMIN-003</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Admin Content Configuration</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Verify Admin B2B Holds View &amp; Modify Action Content Customization</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Admin logged in under Stores &gt; Configuration &gt; Customer Account Content Configs.</v>
+      </c>
+      <c r="F34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. In B2b Account Content section, locate B2b Holds View Title, B2b Holds View Text, B2b Holds Modify Title, and B2b Holds Modify Text
+2. Uncheck Use system value
+3. Input custom instructional text for viewing and modifying active holds
+4. Click Save Config and verify database persistence</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Admin provides editable text configuration to manage customer instructions for Viewing and Modifying/Confirming holds.</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Configuration fields are present and accept custom instructional strings for holds view and modify workflows.</v>
+      </c>
+      <c r="I34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J34" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Frame 621 Holds Flow Spec</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>TC-GW-HOLDS-ADMIN-004</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Admin Dashboard Integration</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Verify Admin Toggle to Enable/Disable Holds Widget on Customer Dashboard</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Admin user in Stores &gt; Configuration &gt; OVERDOSE &gt; Customer Account Content Configs.</v>
+      </c>
+      <c r="F35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Expand Hidden blocks of the dashboard fieldset
+2. Locate Is Show Holds Block dropdown
+3. Toggle between Yes and No
+4. Click Save Config and flush cache
+5. Navigate to frontend /customer/account/ to verify Holds summary widget visibility</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Setting Is Show Holds Block to Yes displays the active holds reservation widget on the My Account dashboard; setting to No hides it cleanly.</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Admin toggle functions correctly; controls visibility of the Holds card on the customer dashboard.</v>
+      </c>
+      <c r="I35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J35" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Dashboard Modular Architecture</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>TC-GW-HOLDS-ADMIN-005</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Admin Content Configuration</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Verify Admin Ability to Configure Support Phone &amp; Email for USA Scope [DEFECT]</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Admin user in Stores &gt; Configuration &gt; Customer Account Content Configs under USA Scope.</v>
+      </c>
+      <c r="F36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open Stores &gt; Configuration &gt; Overdose &gt; Customer Account Content Configs
+2. Scroll to B2b Help Block Hold Orders section
+3. Inspect Phone Number and Email fields
+4. Compare with frontend support block display on /gw_orders/hold/index/</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Admin allows configuring a US domestic toll-free phone number (+1 800-XXX-XXXX) and US email (sales@globewest.com) isolated to USA Website scope.</v>
+      </c>
+      <c r="H36" t="str">
+        <v>FAIL: Configured values leak Australian contact details (Phone: +613 9518 1600, Email: sales@globewest.com.au) on the US storefront.</v>
+      </c>
+      <c r="I36" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="J36" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K36" t="str">
+        <v>US Storefront Localization</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>TC-GW-HOLDS-ADMIN-006</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Admin NetSuite ERP Sync</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Verify NetSuite Connector ERP Queue &amp; 2-Business-Day Inventory Reservation Sync</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Trade customer places a product hold on US storefront (mcstaging2.globewest.com/gw_orders/hold/index/).</v>
+      </c>
+      <c r="F37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. In Admin, navigate to Stores &gt; Configuration &gt; OVERDOSE &gt; Netsuite Connector
+2. Check integration queue status for hold records
+3. Verify customer ID, reserved SKU, item quantity, and 48-hour expiration timestamp sync payload
+4. Verify commercial inventory is reserved in NetSuite</v>
+      </c>
+      <c r="G37" t="str">
+        <v>New hold triggers automated NetSuite API sync, reserves inventory for exactly 2 business days, and records expiration timestamp in ERP queue.</v>
+      </c>
+      <c r="H37" t="str">
+        <v>NetSuite Connector logs show hold sync requests with customer ID and product SKU payload.</v>
+      </c>
+      <c r="I37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J37" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K37" t="str">
+        <v>B2B NetSuite Inventory Architecture</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>TC-GW-HOLDS-ADMIN-007</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Admin Sales Orders Grid</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Verify NetSuite Orders &amp; Holds Grid Lookup in Magento Admin</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Admin logged in; navigate to Sales &gt; Netsuite Orders (/godmode/gw_orders/order/index/).</v>
+      </c>
+      <c r="F38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Sales &gt; Netsuite Orders
+2. Inspect the grid columns (ID, Order Name, Client Name, Purchase Date, Status, Amount, Balance Due)
+3. Filter by trade customer name or hold increment ID
+4. View record details to inspect line items and reservation status</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Admin grid displays trade customer order and hold records accurately, providing search and status lookup.</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Netsuite Orders grid loads with full columns and filtering capabilities.</v>
+      </c>
+      <c r="I38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J38" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Magento Admin Sales Management</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>TC-GW-HOLDS-ADMIN-008</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Admin Automated Cron</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Magento Admin / Cron</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Verify Automated Hold Expiration Cron Job Execution &amp; Real-Time Tab Transition</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Hold record exceeding 2 business days expiration window.</v>
+      </c>
+      <c r="F39" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Execute or observe automated cron job (gw_orders_expire_holds)
+2. Check hold status transition in database/Admin
+3. Navigate to frontend /gw_orders/hold/index/ as Trade customer
+4. Verify hold moves from ACTIVE tab to INACTIVE tab and inventory is released</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Cron identifies expired holds, updates status to "Expired", releases reserved stock back to NetSuite inventory, and shifts row to INACTIVE tab on frontend.</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Cron transitions expired hold records automatically; frontend reflects transition cleanly.</v>
+      </c>
+      <c r="I39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J39" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Automated Inventory Lifecycle</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>TC-GW-HOLDS-ADMIN-009</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Admin Content Configuration</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Verify Admin Holds FAQ CMS Block Configuration via Adobe Commerce Page Builder</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Admin user in Content &gt; Elements &gt; Blocks.</v>
+      </c>
+      <c r="F40" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Content &gt; Elements &gt; Blocks
+2. Search identifier: account_holds_faq
+3. Click Edit on the block
+4. Click "Edit with Page Builder" to expand workspace
+5. Inspect ul[data-content-type=faq] container and existing li[data-content-type=faq-item] accordions</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Admin CMS Block uses Adobe Commerce Page Builder with modular FAQ container (data-content-type=faq) and FAQ Item elements.</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Page Builder workspace loads and displays editable FAQ accordion elements.</v>
+      </c>
+      <c r="I40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J40" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Frame 621 FAQ Admin Spec</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>TC-GW-HOLDS-ADMIN-010</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Admin Content Configuration</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Verify Step-by-Step Procedure to Add a New Holds FAQ Item &amp; Enforce 8-Item Limit</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Admin user in Page Builder workspace for account_holds_faq block under USA Website scope.</v>
+      </c>
+      <c r="F41" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. In Page Builder, drag or click "+" to add a new FAQ Item (data-content-type=faq-item)
+2. Click Settings (Gear Icon) on the item
+3. Enter Question Title (e.g. "Can I extend my hold reservation past 2 days?")
+4. In WYSIWYG editor, enter detailed answer text
+5. Set numeric Sort Order and ensure Enable Item = Yes
+6. Verify total question count does not exceed 8 items
+7. Save item, Close Full Screen, and click Save Block
+8. Flush Magento Cache (System &gt; Cache Management)
+9. Verify frontend reflection on /gw_orders/hold/index/</v>
+      </c>
+      <c r="G41" t="str">
+        <v>New FAQ item created in Admin Page Builder, deployed to US storefront, renders closed by default, expands properly on click, auto-collapses previous item, and adheres to &lt;= 8 ceiling.</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Admin Page Builder supports adding FAQ items; new question reflects on frontend accordion following cache flush with full single-open parity.</v>
+      </c>
+      <c r="I41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J41" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Frame 621 FAQ Admin Spec</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>TC-GW-HOLDS-ADMIN-011</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Admin Cache Management</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Verify Admin Cache Management &amp; Instant Frontend Propagation for Holds Updates</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Admin saves content update to Holds configuration or CMS block.</v>
+      </c>
+      <c r="F42" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to System &gt; Tools &gt; Cache Management
+2. Select Blocks HTML output, Page Cache, and Configuration
+3. Click "Flush Magento Cache"
+4. Observe confirmation message: "The Magento cache storage has been flushed"
+5. Hard-refresh frontend /gw_orders/hold/index/ in incognito tab</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Flushing Magento cache successfully invalidates stale varnish/FPC cache and immediately renders updated Holds copy, support info, and FAQ items.</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Cache flush completes successfully; frontend immediately reflects newly published content.</v>
+      </c>
+      <c r="I42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J42" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Cache Invalidation &amp; Content Freshness</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>TC-GW-HOLDS-ADMIN-012</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Admin Scope &amp; Store View Override</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Verify "Use System Value" Uncheck Behavior for USA Store View Overrides</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Admin user in Stores &gt; Configuration under USA Website scope.</v>
+      </c>
+      <c r="F43" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. In Stores &gt; Configuration &gt; Customer Account Content Configs, switch Scope to USA Website
+2. Observe "Use system value" checkboxes next to B2b Holds Title, B2b Holds Text, Phone Number, and Email
+3. Uncheck "Use system value" to enable input editing for USA scope
+4. Enter US-specific values and click Save Config
+5. Switch scope to Main Website (AU) and verify AU global defaults remain untouched</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Unchecking "Use system value" isolates the override to USA Website only; AU baseline configuration remains completely unaffected.</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Scope inheritance and field-level unchecking function properly in Magento 2 core configuration.</v>
+      </c>
+      <c r="I43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J43" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="K43" t="str">
+        <v>AGENTS.md Rule 3 Dual-Storefront Architecture</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Sprint-3/Ticket_41794528_My_Account_Holds/My_Holds_Test_Cases.xlsx
+++ b/Sprint-3/Ticket_41794528_My_Account_Holds/My_Holds_Test_Cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Holds Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="My Holds QA" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K31"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
+    <col min="5" max="5" width="38.83203125" customWidth="1"/>
+    <col min="6" max="6" width="48.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="32.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -556,21 +569,21 @@
         <v>Trade Customer (Logged In)</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify Hold Count Badge Math and Pill Display (Developer Update)</v>
+        <v>Verify Hold Count Badge Math and Pill Display</v>
       </c>
       <c r="E5" t="str">
         <v>Trade Customer with 3 Active Holds and 2 Inactive Holds on record</v>
       </c>
       <c r="F5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect the blue count badge (.item__counter) rendered adjacent to 'Holds' in left navigation
+        <v xml:space="preserve">1. Inspect the count badge (.item__counter) rendered adjacent to 'Holds' in left navigation
 2. Verify displayed numeric value
 3. Check border-radius pill styling</v>
       </c>
       <c r="G5" t="str">
-        <v>Badge renders total count '5' (sum of 3 Active + 2 Inactive holds) in a pill-shaped container, verifying developer Vinod's badge update.</v>
+        <v>Badge renders total count '5' (sum of 3 Active + 2 Inactive holds) in a pill-shaped container matching Figma design.</v>
       </c>
       <c r="H5" t="str">
-        <v>Badge renders '5' inside .item__counter matching total holds count. Verified fixed.</v>
+        <v>Badge renders '5' inside .item__counter matching total holds count.</v>
       </c>
       <c r="I5" t="str">
         <v>PASS</v>
@@ -1529,476 +1542,9 @@
         <v>Global Navigation Standard</v>
       </c>
     </row>
-    <row r="32" xml:space="preserve">
-      <c r="A32" t="str">
-        <v>TC-GW-HOLDS-ADMIN-001</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Admin Authentication &amp; Scope</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Verify Magento Admin Login &amp; USA Website Scope Isolation for Holds Management</v>
-      </c>
-      <c r="E32" t="str">
-        <v>Valid Magento Admin credentials (deepali.londhe@overdose.digital / 2Ho770ZEeX7v).</v>
-      </c>
-      <c r="F32" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to https://mcstaging2.globewest.com.au/godmode/admin/
-2. Enter authorized credentials and submit
-3. Verify successful redirect to Admin Dashboard
-4. Click Scope switcher dropdown in header
-5. Select USA Website / USA Store View and confirm active scope header</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Admin authenticates successfully; scope switcher allows switching to USA Website to isolate US market configuration from Australian baseline.</v>
-      </c>
-      <c r="H32" t="str">
-        <v>Admin login verified functional; USA Website scope switcher is active and selectable.</v>
-      </c>
-      <c r="I32" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J32" t="str">
-        <v>P1 - High</v>
-      </c>
-      <c r="K32" t="str">
-        <v>AGENTS.md Rule 3 Dual-Store Scope</v>
-      </c>
-    </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33" t="str">
-        <v>TC-GW-HOLDS-ADMIN-002</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Admin Content Configuration</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Verify Admin Holds Title &amp; Subtitle Copy Configuration and US Spelling Localization [DEFECT]</v>
-      </c>
-      <c r="E33" t="str">
-        <v>Admin logged in under USA Website scope.</v>
-      </c>
-      <c r="F33" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to Stores &gt; Configuration &gt; OVERDOSE &gt; Customer Account Content Configs
-2. Expand B2b Account Content fieldset
-3. Locate B2b Holds Title and B2b Holds Text fields
-4. Inspect current configured string for B2b Holds Text
-5. Compare with frontend /gw_orders/hold/index/ subtitle copy</v>
-      </c>
-      <c r="G33" t="str">
-        <v>Admin provides dedicated editable fields for Holds title and subtitle; copy for USA scope must use US English spelling (favorite instead of Australian favourite).</v>
-      </c>
-      <c r="H33" t="str">
-        <v>FAIL: Admin configuration currently contains Australian spelling: "A product hold reserves your favourite items for 2 business days...", which leaks directly to US storefront.</v>
-      </c>
-      <c r="I33" t="str">
-        <v>FAIL 🔴</v>
-      </c>
-      <c r="J33" t="str">
-        <v>P2 - Medium</v>
-      </c>
-      <c r="K33" t="str">
-        <v>US Storefront Editorial Localization</v>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34" t="str">
-        <v>TC-GW-HOLDS-ADMIN-003</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Admin Content Configuration</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Verify Admin B2B Holds View &amp; Modify Action Content Customization</v>
-      </c>
-      <c r="E34" t="str">
-        <v>Admin logged in under Stores &gt; Configuration &gt; Customer Account Content Configs.</v>
-      </c>
-      <c r="F34" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. In B2b Account Content section, locate B2b Holds View Title, B2b Holds View Text, B2b Holds Modify Title, and B2b Holds Modify Text
-2. Uncheck Use system value
-3. Input custom instructional text for viewing and modifying active holds
-4. Click Save Config and verify database persistence</v>
-      </c>
-      <c r="G34" t="str">
-        <v>Admin provides editable text configuration to manage customer instructions for Viewing and Modifying/Confirming holds.</v>
-      </c>
-      <c r="H34" t="str">
-        <v>Configuration fields are present and accept custom instructional strings for holds view and modify workflows.</v>
-      </c>
-      <c r="I34" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J34" t="str">
-        <v>P2 - Medium</v>
-      </c>
-      <c r="K34" t="str">
-        <v>Frame 621 Holds Flow Spec</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str">
-        <v>TC-GW-HOLDS-ADMIN-004</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Admin Dashboard Integration</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Verify Admin Toggle to Enable/Disable Holds Widget on Customer Dashboard</v>
-      </c>
-      <c r="E35" t="str">
-        <v>Admin user in Stores &gt; Configuration &gt; OVERDOSE &gt; Customer Account Content Configs.</v>
-      </c>
-      <c r="F35" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Expand Hidden blocks of the dashboard fieldset
-2. Locate Is Show Holds Block dropdown
-3. Toggle between Yes and No
-4. Click Save Config and flush cache
-5. Navigate to frontend /customer/account/ to verify Holds summary widget visibility</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Setting Is Show Holds Block to Yes displays the active holds reservation widget on the My Account dashboard; setting to No hides it cleanly.</v>
-      </c>
-      <c r="H35" t="str">
-        <v>Admin toggle functions correctly; controls visibility of the Holds card on the customer dashboard.</v>
-      </c>
-      <c r="I35" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J35" t="str">
-        <v>P2 - Medium</v>
-      </c>
-      <c r="K35" t="str">
-        <v>Dashboard Modular Architecture</v>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36" t="str">
-        <v>TC-GW-HOLDS-ADMIN-005</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Admin Content Configuration</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Verify Admin Ability to Configure Support Phone &amp; Email for USA Scope [DEFECT]</v>
-      </c>
-      <c r="E36" t="str">
-        <v>Admin user in Stores &gt; Configuration &gt; Customer Account Content Configs under USA Scope.</v>
-      </c>
-      <c r="F36" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open Stores &gt; Configuration &gt; Overdose &gt; Customer Account Content Configs
-2. Scroll to B2b Help Block Hold Orders section
-3. Inspect Phone Number and Email fields
-4. Compare with frontend support block display on /gw_orders/hold/index/</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Admin allows configuring a US domestic toll-free phone number (+1 800-XXX-XXXX) and US email (sales@globewest.com) isolated to USA Website scope.</v>
-      </c>
-      <c r="H36" t="str">
-        <v>FAIL: Configured values leak Australian contact details (Phone: +613 9518 1600, Email: sales@globewest.com.au) on the US storefront.</v>
-      </c>
-      <c r="I36" t="str">
-        <v>FAIL 🔴</v>
-      </c>
-      <c r="J36" t="str">
-        <v>P1 - High</v>
-      </c>
-      <c r="K36" t="str">
-        <v>US Storefront Localization</v>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37" t="str">
-        <v>TC-GW-HOLDS-ADMIN-006</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Admin NetSuite ERP Sync</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Verify NetSuite Connector ERP Queue &amp; 2-Business-Day Inventory Reservation Sync</v>
-      </c>
-      <c r="E37" t="str">
-        <v>Trade customer places a product hold on US storefront (mcstaging2.globewest.com/gw_orders/hold/index/).</v>
-      </c>
-      <c r="F37" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. In Admin, navigate to Stores &gt; Configuration &gt; OVERDOSE &gt; Netsuite Connector
-2. Check integration queue status for hold records
-3. Verify customer ID, reserved SKU, item quantity, and 48-hour expiration timestamp sync payload
-4. Verify commercial inventory is reserved in NetSuite</v>
-      </c>
-      <c r="G37" t="str">
-        <v>New hold triggers automated NetSuite API sync, reserves inventory for exactly 2 business days, and records expiration timestamp in ERP queue.</v>
-      </c>
-      <c r="H37" t="str">
-        <v>NetSuite Connector logs show hold sync requests with customer ID and product SKU payload.</v>
-      </c>
-      <c r="I37" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J37" t="str">
-        <v>P1 - High</v>
-      </c>
-      <c r="K37" t="str">
-        <v>B2B NetSuite Inventory Architecture</v>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str">
-        <v>TC-GW-HOLDS-ADMIN-007</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Admin Sales Orders Grid</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Verify NetSuite Orders &amp; Holds Grid Lookup in Magento Admin</v>
-      </c>
-      <c r="E38" t="str">
-        <v>Admin logged in; navigate to Sales &gt; Netsuite Orders (/godmode/gw_orders/order/index/).</v>
-      </c>
-      <c r="F38" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to Sales &gt; Netsuite Orders
-2. Inspect the grid columns (ID, Order Name, Client Name, Purchase Date, Status, Amount, Balance Due)
-3. Filter by trade customer name or hold increment ID
-4. View record details to inspect line items and reservation status</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Admin grid displays trade customer order and hold records accurately, providing search and status lookup.</v>
-      </c>
-      <c r="H38" t="str">
-        <v>Netsuite Orders grid loads with full columns and filtering capabilities.</v>
-      </c>
-      <c r="I38" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J38" t="str">
-        <v>P2 - Medium</v>
-      </c>
-      <c r="K38" t="str">
-        <v>Magento Admin Sales Management</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
-        <v>TC-GW-HOLDS-ADMIN-008</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Admin Automated Cron</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Magento Admin / Cron</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Verify Automated Hold Expiration Cron Job Execution &amp; Real-Time Tab Transition</v>
-      </c>
-      <c r="E39" t="str">
-        <v>Hold record exceeding 2 business days expiration window.</v>
-      </c>
-      <c r="F39" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Execute or observe automated cron job (gw_orders_expire_holds)
-2. Check hold status transition in database/Admin
-3. Navigate to frontend /gw_orders/hold/index/ as Trade customer
-4. Verify hold moves from ACTIVE tab to INACTIVE tab and inventory is released</v>
-      </c>
-      <c r="G39" t="str">
-        <v>Cron identifies expired holds, updates status to "Expired", releases reserved stock back to NetSuite inventory, and shifts row to INACTIVE tab on frontend.</v>
-      </c>
-      <c r="H39" t="str">
-        <v>Cron transitions expired hold records automatically; frontend reflects transition cleanly.</v>
-      </c>
-      <c r="I39" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J39" t="str">
-        <v>P1 - High</v>
-      </c>
-      <c r="K39" t="str">
-        <v>Automated Inventory Lifecycle</v>
-      </c>
-    </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40" t="str">
-        <v>TC-GW-HOLDS-ADMIN-009</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Admin Content Configuration</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Verify Admin Holds FAQ CMS Block Configuration via Adobe Commerce Page Builder</v>
-      </c>
-      <c r="E40" t="str">
-        <v>Admin user in Content &gt; Elements &gt; Blocks.</v>
-      </c>
-      <c r="F40" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to Content &gt; Elements &gt; Blocks
-2. Search identifier: account_holds_faq
-3. Click Edit on the block
-4. Click "Edit with Page Builder" to expand workspace
-5. Inspect ul[data-content-type=faq] container and existing li[data-content-type=faq-item] accordions</v>
-      </c>
-      <c r="G40" t="str">
-        <v>Admin CMS Block uses Adobe Commerce Page Builder with modular FAQ container (data-content-type=faq) and FAQ Item elements.</v>
-      </c>
-      <c r="H40" t="str">
-        <v>Page Builder workspace loads and displays editable FAQ accordion elements.</v>
-      </c>
-      <c r="I40" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J40" t="str">
-        <v>P2 - Medium</v>
-      </c>
-      <c r="K40" t="str">
-        <v>Frame 621 FAQ Admin Spec</v>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41" t="str">
-        <v>TC-GW-HOLDS-ADMIN-010</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Admin Content Configuration</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Verify Step-by-Step Procedure to Add a New Holds FAQ Item &amp; Enforce 8-Item Limit</v>
-      </c>
-      <c r="E41" t="str">
-        <v>Admin user in Page Builder workspace for account_holds_faq block under USA Website scope.</v>
-      </c>
-      <c r="F41" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. In Page Builder, drag or click "+" to add a new FAQ Item (data-content-type=faq-item)
-2. Click Settings (Gear Icon) on the item
-3. Enter Question Title (e.g. "Can I extend my hold reservation past 2 days?")
-4. In WYSIWYG editor, enter detailed answer text
-5. Set numeric Sort Order and ensure Enable Item = Yes
-6. Verify total question count does not exceed 8 items
-7. Save item, Close Full Screen, and click Save Block
-8. Flush Magento Cache (System &gt; Cache Management)
-9. Verify frontend reflection on /gw_orders/hold/index/</v>
-      </c>
-      <c r="G41" t="str">
-        <v>New FAQ item created in Admin Page Builder, deployed to US storefront, renders closed by default, expands properly on click, auto-collapses previous item, and adheres to &lt;= 8 ceiling.</v>
-      </c>
-      <c r="H41" t="str">
-        <v>Admin Page Builder supports adding FAQ items; new question reflects on frontend accordion following cache flush with full single-open parity.</v>
-      </c>
-      <c r="I41" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J41" t="str">
-        <v>P2 - Medium</v>
-      </c>
-      <c r="K41" t="str">
-        <v>Frame 621 FAQ Admin Spec</v>
-      </c>
-    </row>
-    <row r="42" xml:space="preserve">
-      <c r="A42" t="str">
-        <v>TC-GW-HOLDS-ADMIN-011</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Admin Cache Management</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Verify Admin Cache Management &amp; Instant Frontend Propagation for Holds Updates</v>
-      </c>
-      <c r="E42" t="str">
-        <v>Admin saves content update to Holds configuration or CMS block.</v>
-      </c>
-      <c r="F42" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to System &gt; Tools &gt; Cache Management
-2. Select Blocks HTML output, Page Cache, and Configuration
-3. Click "Flush Magento Cache"
-4. Observe confirmation message: "The Magento cache storage has been flushed"
-5. Hard-refresh frontend /gw_orders/hold/index/ in incognito tab</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Flushing Magento cache successfully invalidates stale varnish/FPC cache and immediately renders updated Holds copy, support info, and FAQ items.</v>
-      </c>
-      <c r="H42" t="str">
-        <v>Cache flush completes successfully; frontend immediately reflects newly published content.</v>
-      </c>
-      <c r="I42" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J42" t="str">
-        <v>P2 - Medium</v>
-      </c>
-      <c r="K42" t="str">
-        <v>Cache Invalidation &amp; Content Freshness</v>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str">
-        <v>TC-GW-HOLDS-ADMIN-012</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Admin Scope &amp; Store View Override</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Magento Admin User</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Verify "Use System Value" Uncheck Behavior for USA Store View Overrides</v>
-      </c>
-      <c r="E43" t="str">
-        <v>Admin user in Stores &gt; Configuration under USA Website scope.</v>
-      </c>
-      <c r="F43" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. In Stores &gt; Configuration &gt; Customer Account Content Configs, switch Scope to USA Website
-2. Observe "Use system value" checkboxes next to B2b Holds Title, B2b Holds Text, Phone Number, and Email
-3. Uncheck "Use system value" to enable input editing for USA scope
-4. Enter US-specific values and click Save Config
-5. Switch scope to Main Website (AU) and verify AU global defaults remain untouched</v>
-      </c>
-      <c r="G43" t="str">
-        <v>Unchecking "Use system value" isolates the override to USA Website only; AU baseline configuration remains completely unaffected.</v>
-      </c>
-      <c r="H43" t="str">
-        <v>Scope inheritance and field-level unchecking function properly in Magento 2 core configuration.</v>
-      </c>
-      <c r="I43" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="J43" t="str">
-        <v>P1 - High</v>
-      </c>
-      <c r="K43" t="str">
-        <v>AGENTS.md Rule 3 Dual-Storefront Architecture</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
   </ignoredErrors>
 </worksheet>
 </file>